--- a/misc/modélisation TB.xlsx
+++ b/misc/modélisation TB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priol\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Sauvegarde PROG\BGA Studio\toybattle\misc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D063EC2F-D139-4CDE-A715-EAB04ED1AC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF625D3-FCC2-41DD-A796-F7BB8C833D3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23190" yWindow="3705" windowWidth="12615" windowHeight="15240" xr2:uid="{F62B89E2-EC14-40E3-9689-D978C6593047}"/>
+    <workbookView xWindow="16650" yWindow="3705" windowWidth="19155" windowHeight="15240" xr2:uid="{F62B89E2-EC14-40E3-9689-D978C6593047}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -110,12 +110,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -123,6 +117,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -463,56 +463,56 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
       <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="K1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
       <c r="Q1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
+      <c r="T1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
       <c r="Z1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="AB1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="AC1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="2"/>
+      <c r="AC1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
       <c r="AI1" s="1" t="s">
         <v>2</v>
       </c>
@@ -1620,695 +1620,695 @@
       <c r="AI18" s="1"/>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>2</v>
-      </c>
-      <c r="Z19" s="6">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>2</v>
+      </c>
+      <c r="Z19" s="4">
         <v>6</v>
       </c>
-      <c r="AI19" s="6">
+      <c r="AI19" s="4">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="3" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="3" t="s">
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="S20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="T20" s="4" t="s">
+      <c r="T20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="U20" s="4"/>
-      <c r="V20" s="4"/>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="3" t="s">
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AB20" s="3" t="s">
+      <c r="AB20" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AC20" s="4" t="s">
+      <c r="AC20" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="AD20" s="4"/>
-      <c r="AE20" s="4"/>
-      <c r="AF20" s="4"/>
-      <c r="AG20" s="4"/>
-      <c r="AH20" s="4"/>
-      <c r="AI20" s="3" t="s">
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
+      <c r="AG20" s="6"/>
+      <c r="AH20" s="6"/>
+      <c r="AI20" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
+      <c r="A21" s="3">
         <v>31</v>
       </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5">
-        <v>2</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="B21" s="3">
+        <v>1</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3">
         <v>3</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="3">
         <v>4</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="3">
         <v>5</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="3">
         <v>9</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="3">
         <v>3</v>
       </c>
-      <c r="J21" s="5">
-        <v>11</v>
-      </c>
-      <c r="K21" s="5">
-        <v>11</v>
-      </c>
-      <c r="L21" s="5">
-        <v>12</v>
-      </c>
-      <c r="M21" s="5">
-        <v>13</v>
-      </c>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5">
-        <v>1</v>
-      </c>
-      <c r="S21" s="5">
-        <v>11</v>
-      </c>
-      <c r="T21" s="5">
-        <v>1</v>
-      </c>
-      <c r="U21" s="5">
-        <v>11</v>
-      </c>
-      <c r="V21" s="5">
-        <v>13</v>
-      </c>
-      <c r="W21" s="5">
-        <v>14</v>
-      </c>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="5">
-        <v>11</v>
-      </c>
-      <c r="AC21" s="5">
-        <v>12</v>
-      </c>
-      <c r="AD21" s="5">
-        <v>13</v>
-      </c>
-      <c r="AE21" s="5">
-        <v>15</v>
-      </c>
-      <c r="AF21" s="5"/>
-      <c r="AG21" s="5"/>
-      <c r="AH21" s="5"/>
-      <c r="AI21" s="5">
+      <c r="J21" s="3">
+        <v>11</v>
+      </c>
+      <c r="K21" s="3">
+        <v>11</v>
+      </c>
+      <c r="L21" s="3">
+        <v>12</v>
+      </c>
+      <c r="M21" s="3">
+        <v>13</v>
+      </c>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3">
+        <v>1</v>
+      </c>
+      <c r="S21" s="3">
+        <v>11</v>
+      </c>
+      <c r="T21" s="3">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3">
+        <v>11</v>
+      </c>
+      <c r="V21" s="3">
+        <v>13</v>
+      </c>
+      <c r="W21" s="3">
+        <v>14</v>
+      </c>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="3">
+        <v>11</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>12</v>
+      </c>
+      <c r="AD21" s="3">
+        <v>13</v>
+      </c>
+      <c r="AE21" s="3">
+        <v>15</v>
+      </c>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>11</v>
-      </c>
-      <c r="B22" s="5">
+      <c r="A22" s="3">
+        <v>11</v>
+      </c>
+      <c r="B22" s="3">
         <v>4</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="3">
         <v>6</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="3">
         <v>8</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5">
-        <v>1</v>
-      </c>
-      <c r="J22" s="5">
-        <v>21</v>
-      </c>
-      <c r="K22" s="5">
-        <v>12</v>
-      </c>
-      <c r="L22" s="5">
-        <v>13</v>
-      </c>
-      <c r="M22" s="5">
-        <v>15</v>
-      </c>
-      <c r="N22" s="5">
-        <v>17</v>
-      </c>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5">
-        <v>2</v>
-      </c>
-      <c r="S22" s="5">
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3">
+        <v>21</v>
+      </c>
+      <c r="K22" s="3">
+        <v>12</v>
+      </c>
+      <c r="L22" s="3">
+        <v>13</v>
+      </c>
+      <c r="M22" s="3">
+        <v>15</v>
+      </c>
+      <c r="N22" s="3">
+        <v>17</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3">
+        <v>2</v>
+      </c>
+      <c r="S22" s="3">
         <v>31</v>
       </c>
-      <c r="T22" s="5">
-        <v>11</v>
-      </c>
-      <c r="U22" s="5">
-        <v>12</v>
-      </c>
-      <c r="V22" s="5">
-        <v>14</v>
-      </c>
-      <c r="W22" s="5">
-        <v>16</v>
-      </c>
-      <c r="X22" s="5">
-        <v>17</v>
-      </c>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5">
+      <c r="T22" s="3">
+        <v>11</v>
+      </c>
+      <c r="U22" s="3">
+        <v>12</v>
+      </c>
+      <c r="V22" s="3">
+        <v>14</v>
+      </c>
+      <c r="W22" s="3">
+        <v>16</v>
+      </c>
+      <c r="X22" s="3">
+        <v>17</v>
+      </c>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3">
         <v>3</v>
       </c>
-      <c r="AB22" s="5">
-        <v>21</v>
-      </c>
-      <c r="AC22" s="5">
-        <v>11</v>
-      </c>
-      <c r="AD22" s="5">
-        <v>13</v>
-      </c>
-      <c r="AE22" s="5">
-        <v>15</v>
-      </c>
-      <c r="AF22" s="5">
-        <v>16</v>
-      </c>
-      <c r="AG22" s="5"/>
-      <c r="AH22" s="5"/>
-      <c r="AI22" s="5">
+      <c r="AB22" s="3">
+        <v>21</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>11</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>13</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>15</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>16</v>
+      </c>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A23" s="5">
-        <v>12</v>
-      </c>
-      <c r="B23" s="5">
+      <c r="A23" s="3">
+        <v>12</v>
+      </c>
+      <c r="B23" s="3">
         <v>5</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="3">
         <v>7</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="3">
         <v>10</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5">
-        <v>1</v>
-      </c>
-      <c r="J23" s="5">
-        <v>12</v>
-      </c>
-      <c r="K23" s="5">
-        <v>13</v>
-      </c>
-      <c r="L23" s="5">
-        <v>14</v>
-      </c>
-      <c r="M23" s="5">
-        <v>17</v>
-      </c>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5">
-        <v>1</v>
-      </c>
-      <c r="S23" s="5">
-        <v>21</v>
-      </c>
-      <c r="T23" s="5">
-        <v>16</v>
-      </c>
-      <c r="U23" s="5">
-        <v>17</v>
-      </c>
-      <c r="V23" s="5">
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="J23" s="3">
+        <v>12</v>
+      </c>
+      <c r="K23" s="3">
+        <v>13</v>
+      </c>
+      <c r="L23" s="3">
+        <v>14</v>
+      </c>
+      <c r="M23" s="3">
+        <v>17</v>
+      </c>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3">
+        <v>1</v>
+      </c>
+      <c r="S23" s="3">
+        <v>21</v>
+      </c>
+      <c r="T23" s="3">
+        <v>16</v>
+      </c>
+      <c r="U23" s="3">
+        <v>17</v>
+      </c>
+      <c r="V23" s="3">
         <v>19</v>
       </c>
-      <c r="W23" s="5">
-        <v>20</v>
-      </c>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5">
-        <v>2</v>
-      </c>
-      <c r="AB23" s="5">
-        <v>12</v>
-      </c>
-      <c r="AC23" s="5">
-        <v>11</v>
-      </c>
-      <c r="AD23" s="5">
-        <v>14</v>
-      </c>
-      <c r="AE23" s="5">
-        <v>16</v>
-      </c>
-      <c r="AF23" s="5"/>
-      <c r="AG23" s="5"/>
-      <c r="AH23" s="5"/>
-      <c r="AI23" s="5">
+      <c r="W23" s="3">
+        <v>20</v>
+      </c>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3">
+        <v>2</v>
+      </c>
+      <c r="AB23" s="3">
+        <v>12</v>
+      </c>
+      <c r="AC23" s="3">
+        <v>11</v>
+      </c>
+      <c r="AD23" s="3">
+        <v>14</v>
+      </c>
+      <c r="AE23" s="3">
+        <v>16</v>
+      </c>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>21</v>
-      </c>
-      <c r="B24" s="5">
+      <c r="A24" s="3">
+        <v>21</v>
+      </c>
+      <c r="B24" s="3">
         <v>4</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="3">
         <v>8</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="3">
         <v>9</v>
       </c>
-      <c r="E24" s="5">
-        <v>13</v>
-      </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5">
-        <v>2</v>
-      </c>
-      <c r="J24" s="5">
-        <v>21</v>
-      </c>
-      <c r="K24" s="5">
-        <v>14</v>
-      </c>
-      <c r="L24" s="5">
-        <v>16</v>
-      </c>
-      <c r="M24" s="5">
-        <v>17</v>
-      </c>
-      <c r="N24" s="5">
+      <c r="E24" s="3">
+        <v>13</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3">
+        <v>2</v>
+      </c>
+      <c r="J24" s="3">
+        <v>21</v>
+      </c>
+      <c r="K24" s="3">
+        <v>14</v>
+      </c>
+      <c r="L24" s="3">
+        <v>16</v>
+      </c>
+      <c r="M24" s="3">
+        <v>17</v>
+      </c>
+      <c r="N24" s="3">
         <v>19</v>
       </c>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5">
-        <v>2</v>
-      </c>
-      <c r="S24" s="5">
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3">
+        <v>2</v>
+      </c>
+      <c r="S24" s="3">
         <v>22</v>
       </c>
-      <c r="T24" s="5">
-        <v>12</v>
-      </c>
-      <c r="U24" s="5">
-        <v>17</v>
-      </c>
-      <c r="V24" s="5">
-        <v>20</v>
-      </c>
-      <c r="W24" s="5">
-        <v>21</v>
-      </c>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5">
-        <v>2</v>
-      </c>
-      <c r="AB24" s="5">
-        <v>13</v>
-      </c>
-      <c r="AC24" s="5">
-        <v>15</v>
-      </c>
-      <c r="AD24" s="5">
-        <v>16</v>
-      </c>
-      <c r="AE24" s="5">
+      <c r="T24" s="3">
+        <v>12</v>
+      </c>
+      <c r="U24" s="3">
+        <v>17</v>
+      </c>
+      <c r="V24" s="3">
+        <v>20</v>
+      </c>
+      <c r="W24" s="3">
+        <v>21</v>
+      </c>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3">
+        <v>2</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>13</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>15</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>16</v>
+      </c>
+      <c r="AE24" s="3">
         <v>18</v>
       </c>
-      <c r="AF24" s="5"/>
-      <c r="AG24" s="5"/>
-      <c r="AH24" s="5"/>
-      <c r="AI24" s="5">
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
+      <c r="A25" s="3">
         <v>22</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="3">
         <v>5</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="3">
         <v>9</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="3">
         <v>10</v>
       </c>
-      <c r="E25" s="5">
-        <v>14</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5">
-        <v>2</v>
-      </c>
-      <c r="J25" s="5">
+      <c r="E25" s="3">
+        <v>14</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3">
+        <v>2</v>
+      </c>
+      <c r="J25" s="3">
         <v>23</v>
       </c>
-      <c r="K25" s="5">
-        <v>15</v>
-      </c>
-      <c r="L25" s="5">
-        <v>17</v>
-      </c>
-      <c r="M25" s="5">
+      <c r="K25" s="3">
+        <v>15</v>
+      </c>
+      <c r="L25" s="3">
+        <v>17</v>
+      </c>
+      <c r="M25" s="3">
         <v>18</v>
       </c>
-      <c r="N25" s="5">
-        <v>20</v>
-      </c>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5">
-        <v>2</v>
-      </c>
-      <c r="S25" s="5">
+      <c r="N25" s="3">
+        <v>20</v>
+      </c>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3">
+        <v>2</v>
+      </c>
+      <c r="S25" s="3">
         <v>23</v>
       </c>
-      <c r="T25" s="5">
-        <v>12</v>
-      </c>
-      <c r="U25" s="5">
-        <v>15</v>
-      </c>
-      <c r="V25" s="5">
+      <c r="T25" s="3">
+        <v>12</v>
+      </c>
+      <c r="U25" s="3">
+        <v>15</v>
+      </c>
+      <c r="V25" s="3">
         <v>18</v>
       </c>
-      <c r="W25" s="5">
-        <v>21</v>
-      </c>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5">
-        <v>2</v>
-      </c>
-      <c r="AB25" s="5">
+      <c r="W25" s="3">
+        <v>21</v>
+      </c>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3">
+        <v>2</v>
+      </c>
+      <c r="AB25" s="3">
         <v>22</v>
       </c>
-      <c r="AC25" s="5">
-        <v>15</v>
-      </c>
-      <c r="AD25" s="5">
-        <v>17</v>
-      </c>
-      <c r="AE25" s="5">
+      <c r="AC25" s="3">
+        <v>15</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>17</v>
+      </c>
+      <c r="AE25" s="3">
         <v>18</v>
       </c>
-      <c r="AF25" s="5">
-        <v>20</v>
-      </c>
-      <c r="AG25" s="5"/>
-      <c r="AH25" s="5"/>
-      <c r="AI25" s="5">
+      <c r="AF25" s="3">
+        <v>20</v>
+      </c>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>13</v>
-      </c>
-      <c r="B26" s="5">
+      <c r="A26" s="3">
+        <v>13</v>
+      </c>
+      <c r="B26" s="3">
         <v>8</v>
       </c>
-      <c r="C26" s="5">
-        <v>11</v>
-      </c>
-      <c r="D26" s="5">
-        <v>13</v>
-      </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5">
-        <v>1</v>
-      </c>
-      <c r="J26" s="5">
+      <c r="C26" s="3">
+        <v>11</v>
+      </c>
+      <c r="D26" s="3">
+        <v>13</v>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3">
         <v>24</v>
       </c>
-      <c r="K26" s="5">
-        <v>17</v>
-      </c>
-      <c r="L26" s="5">
-        <v>20</v>
-      </c>
-      <c r="M26" s="5">
-        <v>21</v>
-      </c>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5">
-        <v>2</v>
-      </c>
-      <c r="S26" s="5">
+      <c r="K26" s="3">
+        <v>17</v>
+      </c>
+      <c r="L26" s="3">
+        <v>20</v>
+      </c>
+      <c r="M26" s="3">
+        <v>21</v>
+      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3">
+        <v>2</v>
+      </c>
+      <c r="S26" s="3">
         <v>24</v>
       </c>
-      <c r="T26" s="5">
+      <c r="T26" s="3">
         <v>19</v>
       </c>
-      <c r="U26" s="5">
-        <v>20</v>
-      </c>
-      <c r="V26" s="5">
+      <c r="U26" s="3">
+        <v>20</v>
+      </c>
+      <c r="V26" s="3">
         <v>22</v>
       </c>
-      <c r="W26" s="5">
+      <c r="W26" s="3">
         <v>41</v>
       </c>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
-      <c r="Z26" s="5">
-        <v>2</v>
-      </c>
-      <c r="AB26" s="5">
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3">
+        <v>2</v>
+      </c>
+      <c r="AB26" s="3">
         <v>23</v>
       </c>
-      <c r="AC26" s="5">
-        <v>16</v>
-      </c>
-      <c r="AD26" s="5">
+      <c r="AC26" s="3">
+        <v>16</v>
+      </c>
+      <c r="AD26" s="3">
         <v>18</v>
       </c>
-      <c r="AE26" s="5">
+      <c r="AE26" s="3">
         <v>19</v>
       </c>
-      <c r="AF26" s="5">
-        <v>21</v>
-      </c>
-      <c r="AG26" s="5"/>
-      <c r="AH26" s="5"/>
-      <c r="AI26" s="5">
+      <c r="AF26" s="3">
+        <v>21</v>
+      </c>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>14</v>
-      </c>
-      <c r="B27" s="5">
+      <c r="A27" s="3">
+        <v>14</v>
+      </c>
+      <c r="B27" s="3">
         <v>10</v>
       </c>
-      <c r="C27" s="5">
-        <v>12</v>
-      </c>
-      <c r="D27" s="5">
-        <v>14</v>
-      </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5">
-        <v>1</v>
-      </c>
-      <c r="J27" s="5">
+      <c r="C27" s="3">
+        <v>12</v>
+      </c>
+      <c r="D27" s="3">
+        <v>14</v>
+      </c>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3">
+        <v>1</v>
+      </c>
+      <c r="J27" s="3">
         <v>25</v>
       </c>
-      <c r="K27" s="5">
-        <v>17</v>
-      </c>
-      <c r="L27" s="5">
+      <c r="K27" s="3">
+        <v>17</v>
+      </c>
+      <c r="L27" s="3">
         <v>19</v>
       </c>
-      <c r="M27" s="5">
-        <v>21</v>
-      </c>
-      <c r="N27" s="5">
+      <c r="M27" s="3">
+        <v>21</v>
+      </c>
+      <c r="N27" s="3">
         <v>22</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5">
-        <v>2</v>
-      </c>
-      <c r="AB27" s="5">
-        <v>14</v>
-      </c>
-      <c r="AC27" s="5">
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3">
+        <v>2</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>14</v>
+      </c>
+      <c r="AC27" s="3">
         <v>18</v>
       </c>
-      <c r="AD27" s="5">
-        <v>20</v>
-      </c>
-      <c r="AE27" s="5">
-        <v>21</v>
-      </c>
-      <c r="AI27" s="5">
+      <c r="AD27" s="3">
+        <v>20</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>21</v>
+      </c>
+      <c r="AI27" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+      <c r="A28" s="3">
         <v>32</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="3">
         <v>9</v>
       </c>
-      <c r="C28" s="5">
-        <v>13</v>
-      </c>
-      <c r="D28" s="5">
-        <v>14</v>
-      </c>
-      <c r="E28" s="5">
-        <v>15</v>
-      </c>
-      <c r="F28" s="5">
-        <v>16</v>
-      </c>
-      <c r="G28" s="5">
-        <v>17</v>
-      </c>
-      <c r="H28" s="5">
+      <c r="C28" s="3">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3">
+        <v>14</v>
+      </c>
+      <c r="E28" s="3">
+        <v>15</v>
+      </c>
+      <c r="F28" s="3">
+        <v>16</v>
+      </c>
+      <c r="G28" s="3">
+        <v>17</v>
+      </c>
+      <c r="H28" s="3">
         <v>3</v>
       </c>
-      <c r="J28" s="5">
-        <v>13</v>
-      </c>
-      <c r="K28" s="5">
-        <v>21</v>
-      </c>
-      <c r="L28" s="5">
+      <c r="J28" s="3">
+        <v>13</v>
+      </c>
+      <c r="K28" s="3">
+        <v>21</v>
+      </c>
+      <c r="L28" s="3">
         <v>22</v>
       </c>
-      <c r="M28" s="5">
+      <c r="M28" s="3">
         <v>23</v>
       </c>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="5">
-        <v>15</v>
-      </c>
-      <c r="AC28" s="5">
-        <v>20</v>
-      </c>
-      <c r="AD28" s="5">
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>15</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>20</v>
+      </c>
+      <c r="AD28" s="3">
         <v>22</v>
       </c>
-      <c r="AE28" s="5">
+      <c r="AE28" s="3">
         <v>25</v>
       </c>
-      <c r="AI28" s="5">
+      <c r="AI28" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="AB29" s="5">
+      <c r="AB29" s="3">
         <v>24</v>
       </c>
-      <c r="AC29" s="5">
-        <v>20</v>
-      </c>
-      <c r="AD29" s="5">
-        <v>21</v>
-      </c>
-      <c r="AE29" s="5">
+      <c r="AC29" s="3">
+        <v>20</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>21</v>
+      </c>
+      <c r="AE29" s="3">
         <v>23</v>
       </c>
-      <c r="AF29" s="5">
+      <c r="AF29" s="3">
         <v>25</v>
       </c>
-      <c r="AI29" s="5">
+      <c r="AI29" s="3">
         <v>2</v>
       </c>
     </row>
@@ -2319,19 +2319,19 @@
       <c r="Q30" t="s">
         <v>5</v>
       </c>
-      <c r="AB30" s="5">
-        <v>16</v>
-      </c>
-      <c r="AC30" s="5">
-        <v>21</v>
-      </c>
-      <c r="AD30" s="5">
+      <c r="AB30" s="3">
+        <v>16</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>21</v>
+      </c>
+      <c r="AD30" s="3">
         <v>23</v>
       </c>
-      <c r="AE30" s="5">
+      <c r="AE30" s="3">
         <v>24</v>
       </c>
-      <c r="AI30" s="5">
+      <c r="AI30" s="3">
         <v>1</v>
       </c>
     </row>
